--- a/請求書・見積書/かもめ-フォーラム(Yokusuru)/作業内容.xlsx
+++ b/請求書・見積書/かもめ-フォーラム(Yokusuru)/作業内容.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11207"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10110"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/chikakokunugi/Documents/GitHub/private/請求書・見積書/かもめ-フォーラム(Yokusuru)/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D1375A3D-D6D1-7545-8055-81F12BF5B4BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC365928-D456-1348-97D9-37D705E63715}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="21220" yWindow="-18960" windowWidth="27000" windowHeight="16400" xr2:uid="{FFE5F213-86FF-8441-A6FF-79B8D7AB7854}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="27720" windowHeight="17500" xr2:uid="{FFE5F213-86FF-8441-A6FF-79B8D7AB7854}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="25">
   <si>
     <t>サイト名</t>
     <phoneticPr fontId="1"/>
@@ -118,13 +118,7 @@
       <t>チョウサ</t>
     </rPh>
     <rPh sb="21" eb="23">
-      <t>ケイサイ</t>
-    </rPh>
-    <rPh sb="23" eb="24">
-      <t>ツイカ</t>
-    </rPh>
-    <rPh sb="27" eb="29">
-      <t>ショウヒn</t>
+      <t>ケイサイツイカショウヒn</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -179,6 +173,93 @@
     <t>見積もり金額</t>
     <rPh sb="0" eb="2">
       <t>ミツモリ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>画像リンク切れ修正</t>
+    <rPh sb="0" eb="2">
+      <t>ガゾウ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>シュウセイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>エステ買取コム</t>
+    <rPh sb="0" eb="2">
+      <t>エステ</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>カイトリ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>エステ・コスメ</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>追従ボタンとポップアップの作成・設置</t>
+    <rPh sb="0" eb="2">
+      <t>ツイジュウ</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>サクセイ</t>
+    </rPh>
+    <rPh sb="16" eb="18">
+      <t>セッティ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>エステ買取コム</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t xml:space="preserve">商品追加の反映 nakamura0114esthe </t>
+    <rPh sb="0" eb="2">
+      <t>ショウヒn</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ツイカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t xml:space="preserve">商品追加の反映 nakamura0114ilink </t>
+    <rPh sb="0" eb="2">
+      <t>ショウヒn</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ツイカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>商品追加の反映(makamura0108esthe)と、サイト崩れのコード修正</t>
+    <rPh sb="0" eb="2">
+      <t>ショウヒn</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ツイカ</t>
+    </rPh>
+    <rPh sb="16" eb="18">
+      <t>シュウセイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>商品追加・修正の反映 nakamura1219ilink</t>
+    <rPh sb="0" eb="1">
+      <t>ショウヒn</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>シュウセイ</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>ハンエイ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -567,7 +648,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{25F4BAB4-7167-E048-A0B4-9AB7771B7A95}">
-  <dimension ref="A1:D8"/>
+  <dimension ref="A1:D14"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20"/>
   <cols>
     <col min="2" max="2" width="20.28515625" customWidth="1"/>
@@ -687,6 +768,90 @@
         <v>1500</v>
       </c>
     </row>
+    <row r="9" spans="1:4">
+      <c r="A9" s="1">
+        <v>46373</v>
+      </c>
+      <c r="B9" t="s">
+        <v>8</v>
+      </c>
+      <c r="C9" t="s">
+        <v>16</v>
+      </c>
+      <c r="D9">
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4">
+      <c r="A10" s="1">
+        <v>46031</v>
+      </c>
+      <c r="B10" t="s">
+        <v>8</v>
+      </c>
+      <c r="C10" t="s">
+        <v>24</v>
+      </c>
+      <c r="D10">
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4">
+      <c r="A11" s="1">
+        <v>46031</v>
+      </c>
+      <c r="B11" t="s">
+        <v>17</v>
+      </c>
+      <c r="C11" t="s">
+        <v>23</v>
+      </c>
+      <c r="D11">
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4">
+      <c r="A12" s="1">
+        <v>46041</v>
+      </c>
+      <c r="B12" t="s">
+        <v>18</v>
+      </c>
+      <c r="C12" t="s">
+        <v>19</v>
+      </c>
+      <c r="D12">
+        <v>15000</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4">
+      <c r="A13" s="1">
+        <v>46041</v>
+      </c>
+      <c r="B13" t="s">
+        <v>20</v>
+      </c>
+      <c r="C13" t="s">
+        <v>21</v>
+      </c>
+      <c r="D13">
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4">
+      <c r="A14" s="1">
+        <v>46041</v>
+      </c>
+      <c r="B14" t="s">
+        <v>8</v>
+      </c>
+      <c r="C14" t="s">
+        <v>22</v>
+      </c>
+      <c r="D14">
+        <v>1500</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
